--- a/Sharedpointrequest/Sharedpointrequest/Request/Processing.xlsx
+++ b/Sharedpointrequest/Sharedpointrequest/Request/Processing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA Folders\Migration\Fusion_ICRules\Sharedpointrequest\Sharedpointrequest\Request\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA08A342-44CA-4C97-925D-944C3A0C8E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2BFA48B-2B65-4FB7-92D5-523F0018BF06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7309F474-19F9-4D39-92D5-F7CF120C5A36}"/>
+    <workbookView xWindow="4245" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{7309F474-19F9-4D39-92D5-F7CF120C5A36}"/>
   </bookViews>
   <sheets>
     <sheet name="Processing" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Status - To Update by RPA Team</t>
   </si>
@@ -75,69 +75,6 @@
   </si>
   <si>
     <t>BU</t>
-  </si>
-  <si>
-    <t>Normal</t>
-  </si>
-  <si>
-    <t>SM6</t>
-  </si>
-  <si>
-    <t>Fusion_ICRules</t>
-  </si>
-  <si>
-    <t>Not Started</t>
-  </si>
-  <si>
-    <t>Escorpizo, Paul Vincent (REPH-MNL)</t>
-  </si>
-  <si>
-    <t>Item</t>
-  </si>
-  <si>
-    <t>sites/OG-P2PHdesk/Lists/RequestList</t>
-  </si>
-  <si>
-    <t>Part152-253</t>
-  </si>
-  <si>
-    <t>Part152-253.xlsx</t>
-  </si>
-  <si>
-    <t>Part254-353</t>
-  </si>
-  <si>
-    <t>Part254-353.xlsx</t>
-  </si>
-  <si>
-    <t>Part354-455</t>
-  </si>
-  <si>
-    <t>Part354-455.xlsx</t>
-  </si>
-  <si>
-    <t>Part456-557</t>
-  </si>
-  <si>
-    <t>Part456-557.xlsx</t>
-  </si>
-  <si>
-    <t>Part558-659</t>
-  </si>
-  <si>
-    <t>Part558-659.xlsx</t>
-  </si>
-  <si>
-    <t>Part660-761</t>
-  </si>
-  <si>
-    <t>Part660-761.xlsx</t>
-  </si>
-  <si>
-    <t>Part762-862</t>
-  </si>
-  <si>
-    <t>Part762-862.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1158,304 +1095,150 @@
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="5">
-        <v>10784</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="7">
-        <v>46309.692361111112</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>19</v>
-      </c>
+      <c r="A2" s="5"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
       <c r="L2" s="1" t="str">
         <f t="shared" ref="L2" si="0">IF(A2="","",_xlfn.CONCAT("https://reedelsevier.sharepoint.com/sites/OG-P2PHdesk/Lists/RequestList/Attachments/",A2,"/",I2,"?web=1"))</f>
-        <v>https://reedelsevier.sharepoint.com/sites/OG-P2PHdesk/Lists/RequestList/Attachments/10784/Part152-253.xlsx?web=1</v>
+        <v/>
       </c>
       <c r="M2" s="1" t="str">
         <f t="shared" ref="M2" si="1">IF(A2="","",_xlfn.CONCAT("https://reedelsevier.sharepoint.com/sites/OG-P2PHdesk/Lists/RequestList/DispForm.aspx?ID=",A2))</f>
-        <v>https://reedelsevier.sharepoint.com/sites/OG-P2PHdesk/Lists/RequestList/DispForm.aspx?ID=10784</v>
+        <v/>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
-        <v>10785</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="7">
-        <v>46309.692361111112</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="J3" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>19</v>
-      </c>
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
       <c r="L3" s="1" t="str">
         <f t="shared" ref="L3:L66" si="2">IF(A3="","",_xlfn.CONCAT("https://reedelsevier.sharepoint.com/sites/OG-P2PHdesk/Lists/RequestList/Attachments/",A3,"/",I3,"?web=1"))</f>
-        <v>https://reedelsevier.sharepoint.com/sites/OG-P2PHdesk/Lists/RequestList/Attachments/10785/Part254-353.xlsx?web=1</v>
+        <v/>
       </c>
       <c r="M3" s="1" t="str">
         <f t="shared" ref="M3:M66" si="3">IF(A3="","",_xlfn.CONCAT("https://reedelsevier.sharepoint.com/sites/OG-P2PHdesk/Lists/RequestList/DispForm.aspx?ID=",A3))</f>
-        <v>https://reedelsevier.sharepoint.com/sites/OG-P2PHdesk/Lists/RequestList/DispForm.aspx?ID=10785</v>
+        <v/>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
-        <v>10786</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" s="7">
-        <v>46309.692361111112</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="K4" s="8" t="s">
-        <v>19</v>
-      </c>
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
       <c r="L4" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>https://reedelsevier.sharepoint.com/sites/OG-P2PHdesk/Lists/RequestList/Attachments/10786/Part354-455.xlsx?web=1</v>
+        <v/>
       </c>
       <c r="M4" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>https://reedelsevier.sharepoint.com/sites/OG-P2PHdesk/Lists/RequestList/DispForm.aspx?ID=10786</v>
+        <v/>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
-        <v>10787</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="7">
-        <v>46309.693055555559</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>19</v>
-      </c>
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
       <c r="L5" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>https://reedelsevier.sharepoint.com/sites/OG-P2PHdesk/Lists/RequestList/Attachments/10787/Part456-557.xlsx?web=1</v>
+        <v/>
       </c>
       <c r="M5" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>https://reedelsevier.sharepoint.com/sites/OG-P2PHdesk/Lists/RequestList/DispForm.aspx?ID=10787</v>
+        <v/>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
-        <v>10788</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="G6" s="7">
-        <v>46309.693055555559</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="J6" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="K6" s="8" t="s">
-        <v>19</v>
-      </c>
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
       <c r="L6" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>https://reedelsevier.sharepoint.com/sites/OG-P2PHdesk/Lists/RequestList/Attachments/10788/Part558-659.xlsx?web=1</v>
+        <v/>
       </c>
       <c r="M6" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>https://reedelsevier.sharepoint.com/sites/OG-P2PHdesk/Lists/RequestList/DispForm.aspx?ID=10788</v>
+        <v/>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
-        <v>10789</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7" s="7">
-        <v>46309.693749999999</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="J7" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="K7" s="8" t="s">
-        <v>19</v>
-      </c>
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
       <c r="L7" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>https://reedelsevier.sharepoint.com/sites/OG-P2PHdesk/Lists/RequestList/Attachments/10789/Part660-761.xlsx?web=1</v>
+        <v/>
       </c>
       <c r="M7" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>https://reedelsevier.sharepoint.com/sites/OG-P2PHdesk/Lists/RequestList/DispForm.aspx?ID=10789</v>
+        <v/>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
-        <v>10790</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="G8" s="7">
-        <v>46309.693749999999</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J8" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="K8" s="8" t="s">
-        <v>19</v>
-      </c>
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
       <c r="L8" s="1" t="str">
         <f t="shared" si="2"/>
-        <v>https://reedelsevier.sharepoint.com/sites/OG-P2PHdesk/Lists/RequestList/Attachments/10790/Part762-862.xlsx?web=1</v>
+        <v/>
       </c>
       <c r="M8" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>https://reedelsevier.sharepoint.com/sites/OG-P2PHdesk/Lists/RequestList/DispForm.aspx?ID=10790</v>
+        <v/>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">

--- a/Sharedpointrequest/Sharedpointrequest/Request/Processing.xlsx
+++ b/Sharedpointrequest/Sharedpointrequest/Request/Processing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA Folders\Migration\Fusion_ICRules\Sharedpointrequest\Sharedpointrequest\Request\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2BFA48B-2B65-4FB7-92D5-523F0018BF06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B51AC4C9-CE71-456E-BFCF-D2E73135E8CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4245" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{7309F474-19F9-4D39-92D5-F7CF120C5A36}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7309F474-19F9-4D39-92D5-F7CF120C5A36}"/>
   </bookViews>
   <sheets>
     <sheet name="Processing" sheetId="1" r:id="rId1"/>
